--- a/Grupo Linde/data/Reporte linde VUCE.xlsx
+++ b/Grupo Linde/data/Reporte linde VUCE.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\GitHub\KPI-SIACO\Grupo Linde\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AH20NZZ\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86536F7E-C114-4311-B99D-B0CA8E79712E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{343BE396-9FB3-471B-8331-71E3C9633DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Registros" sheetId="2" r:id="rId1"/>
+    <sheet name="Tracking VUCE" sheetId="1" r:id="rId1"/>
+    <sheet name="Registros" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
@@ -33,39 +34,192 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="90">
   <si>
     <t>CLIENTE</t>
   </si>
   <si>
+    <t>NÚMERO DEL DO</t>
+  </si>
+  <si>
+    <t>NÚMERO DEL DO DE IMPORTACIÓN</t>
+  </si>
+  <si>
+    <t>PROVEEDOR</t>
+  </si>
+  <si>
+    <t>CÓDIGO PRODUCTO</t>
+  </si>
+  <si>
+    <t>ADUANA DE INGRESO</t>
+  </si>
+  <si>
+    <t>CANTIDAD</t>
+  </si>
+  <si>
+    <t>ESTADO VUCE</t>
+  </si>
+  <si>
+    <t>ESTADO DE FACTURACIÓN</t>
+  </si>
+  <si>
+    <t>ESTADO DE LA MERCANCÍA</t>
+  </si>
+  <si>
+    <t>ESTADO DE LA MERCANCÍA PRODUCTO</t>
+  </si>
+  <si>
+    <t>ESTADO DEL REGISTRO</t>
+  </si>
+  <si>
     <t>FECHA DE CREACIÓN</t>
   </si>
   <si>
+    <t>FECHA MODIFICACIÓN</t>
+  </si>
+  <si>
+    <t>PAÍS DE ORIGEN</t>
+  </si>
+  <si>
+    <t>PAÍS DE COMPRA</t>
+  </si>
+  <si>
+    <t>DESCRIPCIÓN</t>
+  </si>
+  <si>
     <t>OXIGENOS DE COLOMBIA LTDA</t>
   </si>
   <si>
+    <t>PRESSURE SOLUTIONS INC</t>
+  </si>
+  <si>
+    <t>5982C32G01,7186A29G06</t>
+  </si>
+  <si>
+    <t>ADUANAS DE BOGOTÁ</t>
+  </si>
+  <si>
+    <t>3.00000,4.00000,5.00000</t>
+  </si>
+  <si>
+    <t>Pte. Revisión</t>
+  </si>
+  <si>
+    <t>NUEVA</t>
+  </si>
+  <si>
+    <t>NUEVO</t>
+  </si>
+  <si>
+    <t>APROBADO</t>
+  </si>
+  <si>
     <t>2026-05-15</t>
   </si>
   <si>
     <t>2026-05-22</t>
   </si>
   <si>
+    <t>ESTADOS UNIDOS DE AMERICA</t>
+  </si>
+  <si>
+    <t>FUSIBLE 5E EATON REF 5BCLS-18R P/N 5982C32G01 5.5 KV,FUSIBLE 5E EATON REF 5NCLPT-5E P/N 7186A29G06 5,5 KV</t>
+  </si>
+  <si>
+    <t>INTERNATIONAL TECHNICSYSTEMS INC</t>
+  </si>
+  <si>
+    <t>053BQ030BZ</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
     <t>2026-05-29</t>
   </si>
   <si>
+    <t>RESMED CORP.</t>
+  </si>
+  <si>
+    <t>14987,19696,19712,19777,19851,36853,37479</t>
+  </si>
+  <si>
     <t>2026-06-02</t>
   </si>
   <si>
+    <t>,FILTRO ENTRADA CPAP RESMED S9 (PAQUETE 50 UNIDS),MAIN PCB - AIRSENSE ELITE PN/: 19851,MAIN PCB-AIRCURVE 10 VAUTO (US),PB ASSYS - AIR10 PN/: 19696,THERAPEUTIC RESPIRATION PARTS &amp; ACCESSORIES</t>
+  </si>
+  <si>
+    <t>LIQUIDO CARBONICO COLOMBIANA S.A.</t>
+  </si>
+  <si>
+    <t>LOGICO2 INTERNATIONAL AB</t>
+  </si>
+  <si>
+    <t>2049,2117</t>
+  </si>
+  <si>
     <t>2026-07-01</t>
   </si>
   <si>
+    <t>SUECIA</t>
+  </si>
+  <si>
+    <t>CO2 MK9 DETECTOR SET 4 A ES,CO2 MK9 SENSOR KIT ES</t>
+  </si>
+  <si>
+    <t>CO2 MK9 DETECTOR SET,CO2 MK9 SENSOR ADD-ON KIT 2117 LOGICO2</t>
+  </si>
+  <si>
+    <t>VAPOTHERM, INC.</t>
+  </si>
+  <si>
+    <t>MI1300,PF-DPC-HIGH,PF-DPC-LOW</t>
+  </si>
+  <si>
     <t>2026-07-07</t>
   </si>
   <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>,INFANT CANNULA. MI1300</t>
+  </si>
+  <si>
+    <t>RESPIRONICS,INC.</t>
+  </si>
+  <si>
+    <t>1038815,1038822,1038825,1038831</t>
+  </si>
+  <si>
+    <t>REQUERIMIENTO</t>
+  </si>
+  <si>
     <t>2026-07-15</t>
   </si>
   <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>,TARJETA P/N 1038815 CONCENTRA DOR RESPIRONICS EVERFLO</t>
+  </si>
+  <si>
+    <t>MI1300</t>
+  </si>
+  <si>
+    <t>VARIAS</t>
+  </si>
+  <si>
+    <t>EN ELABORACIÓN</t>
+  </si>
+  <si>
     <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>INFANT CANNULA. MI1300</t>
   </si>
   <si>
     <t>ESTADO</t>
@@ -495,64 +649,557 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:R9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="40" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="49.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="37.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="30.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="225.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2">
+        <v>2649469</v>
+      </c>
+      <c r="C2">
+        <v>2664491</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2">
+        <v>115</v>
+      </c>
+      <c r="M2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3">
+        <v>2654666</v>
+      </c>
+      <c r="C3">
+        <v>2664001</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3">
+        <v>115</v>
+      </c>
+      <c r="M3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" t="s">
+        <v>33</v>
+      </c>
+      <c r="P3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4">
+        <v>2655844</v>
+      </c>
+      <c r="D4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4">
+        <v>3000</v>
+      </c>
+      <c r="I4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4">
+        <v>115</v>
+      </c>
+      <c r="M4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4" t="s">
+        <v>36</v>
+      </c>
+      <c r="O4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>28</v>
+      </c>
+      <c r="R4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5">
+        <v>2666664</v>
+      </c>
+      <c r="C5">
+        <v>2661520</v>
+      </c>
+      <c r="D5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5">
+        <v>1000</v>
+      </c>
+      <c r="I5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5">
+        <v>115</v>
+      </c>
+      <c r="M5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O5" t="s">
+        <v>41</v>
+      </c>
+      <c r="P5" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>42</v>
+      </c>
+      <c r="R5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
+        <v>2666665</v>
+      </c>
+      <c r="C6">
+        <v>2660815</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6">
+        <v>1000</v>
+      </c>
+      <c r="I6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6">
+        <v>115</v>
+      </c>
+      <c r="M6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N6" t="s">
+        <v>41</v>
+      </c>
+      <c r="O6" t="s">
+        <v>41</v>
+      </c>
+      <c r="P6" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>42</v>
+      </c>
+      <c r="R6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7">
+        <v>2669870</v>
+      </c>
+      <c r="D7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7">
+        <v>1000</v>
+      </c>
+      <c r="I7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7">
+        <v>115</v>
+      </c>
+      <c r="M7" t="s">
+        <v>25</v>
+      </c>
+      <c r="N7" t="s">
+        <v>47</v>
+      </c>
+      <c r="O7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P7" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>28</v>
+      </c>
+      <c r="R7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8">
+        <v>2673313</v>
+      </c>
+      <c r="D8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8">
+        <v>3000</v>
+      </c>
+      <c r="I8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8">
+        <v>113</v>
+      </c>
+      <c r="M8" t="s">
+        <v>52</v>
+      </c>
+      <c r="N8" t="s">
+        <v>53</v>
+      </c>
+      <c r="O8" t="s">
+        <v>54</v>
+      </c>
+      <c r="P8" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>28</v>
+      </c>
+      <c r="R8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>2676144</v>
+      </c>
+      <c r="D9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9">
+        <v>20</v>
+      </c>
+      <c r="I9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9">
+        <v>100</v>
+      </c>
+      <c r="M9" t="s">
+        <v>58</v>
+      </c>
+      <c r="N9" t="s">
+        <v>59</v>
+      </c>
+      <c r="O9" t="s">
+        <v>60</v>
+      </c>
+      <c r="P9" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>28</v>
+      </c>
+      <c r="R9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94761654-2A09-4388-898B-E293E815A559}">
   <dimension ref="A1:H29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="G2">
         <v>20</v>
@@ -561,24 +1208,24 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -587,24 +1234,24 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -613,24 +1260,24 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="F5" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -639,24 +1286,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -665,24 +1312,24 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="G7">
         <v>4</v>
@@ -691,24 +1338,24 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="F8" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="G8">
         <v>10</v>
@@ -717,24 +1364,24 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D9" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="E9" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="F9" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="G9">
         <v>3000</v>
@@ -743,24 +1390,24 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="F10" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="G10">
         <v>3000</v>
@@ -769,24 +1416,24 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="F11" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="G11">
         <v>3000</v>
@@ -795,24 +1442,24 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="E12" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="F12" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="G12">
         <v>3000</v>
@@ -821,24 +1468,24 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="E13" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="F13" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="G13">
         <v>3000</v>
@@ -847,24 +1494,24 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D14" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="E14" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="F14" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="G14">
         <v>3000</v>
@@ -873,24 +1520,24 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="E15" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="F15" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="G15">
         <v>3000</v>
@@ -899,24 +1546,24 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="E16" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="F16" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="G16">
         <v>3000</v>
@@ -925,24 +1572,24 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D17" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="E17" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="F17" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="G17">
         <v>3000</v>
@@ -951,24 +1598,24 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D18" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="E18" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="F18" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="G18">
         <v>1000</v>
@@ -977,24 +1624,24 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D19" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="E19" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="F19" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="G19">
         <v>1000</v>
@@ -1003,24 +1650,24 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E20" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="F20" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="G20">
         <v>1000</v>
@@ -1029,24 +1676,24 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D21" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E21" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="F21" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="G21">
         <v>1000</v>
@@ -1055,24 +1702,24 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D22" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E22" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="F22" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="G22">
         <v>1000</v>
@@ -1081,18 +1728,18 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="E23" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -1101,18 +1748,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D24" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="E24" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -1121,18 +1768,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D25" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="E25" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -1141,18 +1788,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D26" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="E26" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -1161,18 +1808,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D27" t="s">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="E27" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -1181,24 +1828,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C28" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D28" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="E28" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="F28" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="G28">
         <v>1000</v>
@@ -1207,24 +1854,24 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C29" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D29" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="E29" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="F29" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="G29">
         <v>1000</v>
